--- a/specs/spec2.xlsx
+++ b/specs/spec2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SnigdhaYS\Documents\LTSpice_LDO_Automation\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0A7E0A-3854-4F04-8A9C-13302C291B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35764D60-C14B-4349-99B4-528EFA36AFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -246,7 +246,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -256,7 +256,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="31">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -630,202 +629,196 @@
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2">
         <v>1.4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
-        <v>60</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>2E-3</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>50</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10" s="9"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="9">
-        <v>20</v>
-      </c>
-      <c r="C13" s="9"/>
+      <c r="B13">
+        <v>100</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14">
         <v>0</v>
       </c>
-      <c r="C14" s="9"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15">
         <v>1E-3</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16">
         <v>1E-3</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17">
         <v>0.5</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19">
         <v>1000</v>
       </c>
-      <c r="C19" s="9"/>
     </row>
     <row r="24" spans="1:6" ht="26" x14ac:dyDescent="0.6">
       <c r="B24" s="1"/>
